--- a/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
+++ b/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\07_soil_degradation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65F6907-21EB-45D1-B802-F94F7F700E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7134A3AF-9625-409F-ADEA-4F41853615B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle2" sheetId="2" r:id="rId1"/>
@@ -41,10 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="113">
-  <si>
-    <t>Reference</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="115">
   <si>
     <t>SFO</t>
   </si>
@@ -274,9 +271,6 @@
     <t>j.efsa.2008.137r</t>
   </si>
   <si>
-    <t>EFSA PECsoil parameter</t>
-  </si>
-  <si>
     <t>DT50</t>
   </si>
   <si>
@@ -361,9 +355,6 @@
     <t>j.efsa.2015.4206</t>
   </si>
   <si>
-    <t>Worst case lab study DT50</t>
-  </si>
-  <si>
     <t>j.efsa.2023.8012</t>
   </si>
   <si>
@@ -379,7 +370,22 @@
     <t>No pseudo DT50 calculated, as DT90 and DT50 are both &gt;1000d</t>
   </si>
   <si>
-    <t>No DT50 required for PEC soil in 2015 EFSA conclusion, see p44</t>
+    <t>type</t>
+  </si>
+  <si>
+    <t>EFSA PECsoil</t>
+  </si>
+  <si>
+    <t>EFSA LoEP</t>
+  </si>
+  <si>
+    <t>Worst case lab DT50</t>
+  </si>
+  <si>
+    <t>rajo</t>
+  </si>
+  <si>
+    <t>No DT50 required for PEC soil in 2015 EFSA conclusion, see p44, worst-case lab DT50 is from study at 10°C</t>
   </si>
 </sst>
 </file>
@@ -442,7 +448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -452,9 +458,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -739,491 +742,536 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ABC253-0668-4FE2-BC14-84FC263B038A}">
   <dimension ref="A1:Q16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="3" width="8.453125" customWidth="1"/>
-    <col min="4" max="6" width="6.81640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="3" customWidth="1"/>
-    <col min="8" max="9" width="6.81640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="18.453125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24" style="3" customWidth="1"/>
+    <col min="3" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="7" width="6.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="3" customWidth="1"/>
+    <col min="9" max="10" width="6.85546875" style="3" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="8.1796875" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="33.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
       <c r="K2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L2">
         <v>47</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P2" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="K3" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L3" s="4">
         <v>39</v>
       </c>
       <c r="M3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="4">
+        <v>72</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="4">
         <v>20.6</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5"/>
+      <c r="D4" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="K4" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L4" s="4">
         <v>57</v>
       </c>
       <c r="M4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="4">
         <v>226</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5"/>
+      <c r="D5" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="K5" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L5" s="4">
         <v>57</v>
       </c>
       <c r="M5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="7">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="6">
         <v>7.3</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>1</v>
+      <c r="D6" s="5" t="s">
+        <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L6" s="4">
         <v>70</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="4">
+        <v>85</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="4">
         <v>0.1</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>1</v>
+      <c r="D7" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L7" s="4">
         <v>44</v>
       </c>
       <c r="M7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
         <v>83</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" t="s">
-        <v>85</v>
       </c>
       <c r="L8">
         <v>59</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O8" t="s">
+        <v>82</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O8" t="s">
-        <v>84</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9">
+        <v>90</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9">
         <v>28.4</v>
       </c>
-      <c r="C9" t="s">
-        <v>1</v>
+      <c r="D9" t="s">
+        <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L9">
         <v>78</v>
       </c>
       <c r="M9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P9" t="s">
         <v>34</v>
       </c>
-      <c r="N9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10">
+        <v>93</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10">
         <v>98</v>
       </c>
-      <c r="C10" t="s">
-        <v>1</v>
+      <c r="D10" t="s">
+        <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L10">
         <v>34</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P10" t="s">
         <v>34</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="3">
+        <v>94</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="3">
         <v>4.29</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2"/>
+      <c r="D11" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="K11" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L11" s="3">
         <v>56</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N11" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12">
+        <v>96</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12">
         <v>139.5</v>
       </c>
-      <c r="C12" t="s">
-        <v>1</v>
+      <c r="D12" t="s">
+        <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L12">
         <v>41</v>
       </c>
       <c r="M12" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P12" t="s">
         <v>34</v>
       </c>
-      <c r="N12" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13">
+        <v>97</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13">
         <v>184.9</v>
       </c>
-      <c r="C13" t="s">
-        <v>1</v>
+      <c r="D13" t="s">
+        <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L13">
         <v>40</v>
       </c>
       <c r="M13" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P13" t="s">
         <v>34</v>
       </c>
-      <c r="N13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14">
+        <v>98</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14">
         <v>29.6</v>
       </c>
-      <c r="C14" t="s">
-        <v>1</v>
+      <c r="D14" t="s">
+        <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L14">
         <v>37</v>
       </c>
       <c r="M14" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q14" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15">
-        <f>LN(2)/G15</f>
+        <v>99</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15">
+        <f>LN(2)/H15</f>
         <v>533.19013889226562</v>
       </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="3">
         <v>0.20599999999999999</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>0.19139999999999999</v>
       </c>
       <c r="K15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L15">
         <v>33</v>
       </c>
       <c r="M15" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="3">
+      <c r="C16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="3">
         <v>0.18084</v>
       </c>
-      <c r="E16" s="3">
+      <c r="F16" s="3">
         <v>2.6067999999999998</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L16">
         <v>56</v>
       </c>
       <c r="M16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1236,214 +1284,214 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAD96ED-6947-4032-A468-AE450047F46C}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>48</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>50</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>52</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
+++ b/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\07_soil_degradation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6A1019-254D-4E5D-8D85-0DA6AF975297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780B28F6-6BDB-4517-A139-470B676CE7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29085" yWindow="4545" windowWidth="28800" windowHeight="6705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="6195" windowWidth="19275" windowHeight="7245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle2" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="145">
   <si>
     <t>SFO</t>
   </si>
@@ -403,12 +403,6 @@
     <t>j.efsa.2014.3913</t>
   </si>
   <si>
-    <t>EFSA PECsw</t>
-  </si>
-  <si>
-    <t>mean (input for PEC sw)</t>
-  </si>
-  <si>
     <t>median (input for PEC sw)</t>
   </si>
   <si>
@@ -416,6 +410,72 @@
   </si>
   <si>
     <t>Ferric phosphate</t>
+  </si>
+  <si>
+    <t>EFSA PECsw Steps 1-2</t>
+  </si>
+  <si>
+    <t>Geomean (n = 8) SFO after 10mmm rain from normalised field dissipation studies</t>
+  </si>
+  <si>
+    <t>EFSA PECsw Step 3</t>
+  </si>
+  <si>
+    <t>Triclopyr-butotyl</t>
+  </si>
+  <si>
+    <t>EFSA PECgw</t>
+  </si>
+  <si>
+    <t>Conservative DT50 value from the lab study</t>
+  </si>
+  <si>
+    <t>j.efsa.2024.8177_LoEP</t>
+  </si>
+  <si>
+    <t>listed as correct value to be used in future calculations (53.1 d was used in Conclusion)</t>
+  </si>
+  <si>
+    <t>Triclopyr</t>
+  </si>
+  <si>
+    <t>Normalized geomean value from field studies, n = 5</t>
+  </si>
+  <si>
+    <t>Fluroxypyr</t>
+  </si>
+  <si>
+    <t>lab geomean</t>
+  </si>
+  <si>
+    <t>j.efsa.2011.2091</t>
+  </si>
+  <si>
+    <t>Longest normalised laboratory value</t>
+  </si>
+  <si>
+    <t>Longest laboratory corrected only for temperature using Q10 = 2.58</t>
+  </si>
+  <si>
+    <t>MCPB</t>
+  </si>
+  <si>
+    <t>20 °C, aerobic (from 2 to 11.4 days; n = 11)</t>
+  </si>
+  <si>
+    <t>Rewiev Report LoEP</t>
+  </si>
+  <si>
+    <t>physchem</t>
+  </si>
+  <si>
+    <t>Fluroxypyr-meptyl</t>
+  </si>
+  <si>
+    <t>MCPB-sodium</t>
+  </si>
+  <si>
+    <t>MCPB_RR_2005</t>
   </si>
 </sst>
 </file>
@@ -771,21 +831,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ABC253-0668-4FE2-BC14-84FC263B038A}">
-  <dimension ref="A1:Q21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="24" style="3" customWidth="1"/>
-    <col min="3" max="4" width="8.453125" customWidth="1"/>
-    <col min="5" max="7" width="6.81640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" style="3" customWidth="1"/>
-    <col min="9" max="10" width="6.81640625" style="3" customWidth="1"/>
+    <col min="3" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="7" width="6.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="3" customWidth="1"/>
+    <col min="9" max="10" width="6.85546875" style="3" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="8.1796875" customWidth="1"/>
-    <col min="14" max="14" width="33.1796875" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="33.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -838,7 +898,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -867,7 +927,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>86</v>
       </c>
@@ -896,7 +956,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -928,7 +988,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -957,7 +1017,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -989,7 +1049,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -1018,7 +1078,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1047,7 +1107,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -1076,7 +1136,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>93</v>
       </c>
@@ -1105,7 +1165,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>94</v>
       </c>
@@ -1134,7 +1194,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -1163,7 +1223,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>97</v>
       </c>
@@ -1192,7 +1252,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>98</v>
       </c>
@@ -1227,7 +1287,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -1266,7 +1326,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -1304,7 +1364,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>115</v>
       </c>
@@ -1333,12 +1393,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>115</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C18">
         <v>10.19</v>
@@ -1359,15 +1419,15 @@
         <v>111</v>
       </c>
       <c r="O18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P18" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>110</v>
@@ -1394,12 +1454,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -1420,38 +1480,449 @@
         <v>111</v>
       </c>
       <c r="O20" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="P20" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="3">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L21" s="3">
+        <v>56</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="P21" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>24</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K22" t="s">
         <v>116</v>
       </c>
-      <c r="L21">
-        <v>34</v>
-      </c>
-      <c r="M21" t="s">
-        <v>33</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="L22">
+        <v>34</v>
+      </c>
+      <c r="M22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O22" t="s">
         <v>117</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23">
+        <v>28.2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L23">
+        <v>57</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O23" t="s">
+        <v>130</v>
+      </c>
+      <c r="P23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="3">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L24" s="3">
+        <v>59</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O24" t="s">
+        <v>132</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="3">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L25" s="3">
+        <v>65</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L26" s="3">
+        <v>57</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L27" s="3">
+        <v>59</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L28" s="3">
+        <v>63</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29">
+        <v>0.7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L29">
+        <v>49</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O29" t="s">
+        <v>134</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30">
+        <v>13.9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L30">
+        <v>52</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31">
+        <v>1.8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L31">
+        <v>44</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O31" t="s">
+        <v>137</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32">
+        <v>39.6</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L32" s="3">
+        <v>44</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O32" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33">
+        <v>6.8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L33">
+        <v>7</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O33" t="s">
+        <v>139</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L34" s="3">
+        <v>7</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P34" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1465,9 +1936,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAD96ED-6947-4032-A468-AE450047F46C}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -1475,7 +1946,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1483,7 +1954,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -1491,7 +1962,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -1499,7 +1970,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -1507,7 +1978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1515,7 +1986,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1523,7 +1994,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1531,7 +2002,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1539,7 +2010,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1547,7 +2018,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1555,7 +2026,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1563,7 +2034,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1571,7 +2042,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -1579,7 +2050,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1587,7 +2058,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -1595,7 +2066,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -1603,7 +2074,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1611,7 +2082,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1619,7 +2090,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1627,7 +2098,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1635,7 +2106,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -1643,7 +2114,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1651,7 +2122,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -1659,7 +2130,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>68</v>
       </c>
@@ -1667,7 +2138,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>

--- a/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
+++ b/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\07_soil_degradation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7134A3AF-9625-409F-ADEA-4F41853615B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780B28F6-6BDB-4517-A139-470B676CE7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="6195" windowWidth="19275" windowHeight="7245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle2" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="145">
   <si>
     <t>SFO</t>
   </si>
@@ -386,6 +386,96 @@
   </si>
   <si>
     <t>No DT50 required for PEC soil in 2015 EFSA conclusion, see p44, worst-case lab DT50 is from study at 10°C</t>
+  </si>
+  <si>
+    <t>Propamocarb</t>
+  </si>
+  <si>
+    <t>j.efsa.2015.3973</t>
+  </si>
+  <si>
+    <t>no degradation considered</t>
+  </si>
+  <si>
+    <t>j.efsa.2006.78r</t>
+  </si>
+  <si>
+    <t>j.efsa.2014.3913</t>
+  </si>
+  <si>
+    <t>median (input for PEC sw)</t>
+  </si>
+  <si>
+    <t>Halauxifen-methyl</t>
+  </si>
+  <si>
+    <t>Ferric phosphate</t>
+  </si>
+  <si>
+    <t>EFSA PECsw Steps 1-2</t>
+  </si>
+  <si>
+    <t>Geomean (n = 8) SFO after 10mmm rain from normalised field dissipation studies</t>
+  </si>
+  <si>
+    <t>EFSA PECsw Step 3</t>
+  </si>
+  <si>
+    <t>Triclopyr-butotyl</t>
+  </si>
+  <si>
+    <t>EFSA PECgw</t>
+  </si>
+  <si>
+    <t>Conservative DT50 value from the lab study</t>
+  </si>
+  <si>
+    <t>j.efsa.2024.8177_LoEP</t>
+  </si>
+  <si>
+    <t>listed as correct value to be used in future calculations (53.1 d was used in Conclusion)</t>
+  </si>
+  <si>
+    <t>Triclopyr</t>
+  </si>
+  <si>
+    <t>Normalized geomean value from field studies, n = 5</t>
+  </si>
+  <si>
+    <t>Fluroxypyr</t>
+  </si>
+  <si>
+    <t>lab geomean</t>
+  </si>
+  <si>
+    <t>j.efsa.2011.2091</t>
+  </si>
+  <si>
+    <t>Longest normalised laboratory value</t>
+  </si>
+  <si>
+    <t>Longest laboratory corrected only for temperature using Q10 = 2.58</t>
+  </si>
+  <si>
+    <t>MCPB</t>
+  </si>
+  <si>
+    <t>20 °C, aerobic (from 2 to 11.4 days; n = 11)</t>
+  </si>
+  <si>
+    <t>Rewiev Report LoEP</t>
+  </si>
+  <si>
+    <t>physchem</t>
+  </si>
+  <si>
+    <t>Fluroxypyr-meptyl</t>
+  </si>
+  <si>
+    <t>MCPB-sodium</t>
+  </si>
+  <si>
+    <t>MCPB_RR_2005</t>
   </si>
 </sst>
 </file>
@@ -741,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ABC253-0668-4FE2-BC14-84FC263B038A}">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1274,6 +1364,568 @@
         <v>34</v>
       </c>
     </row>
+    <row r="17" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="3">
+        <v>136</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L17" s="3">
+        <v>60</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18">
+        <v>10.19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18">
+        <v>64</v>
+      </c>
+      <c r="M18" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O18" t="s">
+        <v>120</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="3">
+        <v>43</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L19" s="3">
+        <v>56</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20">
+        <v>56</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="3">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L21" s="3">
+        <v>56</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" t="s">
+        <v>116</v>
+      </c>
+      <c r="L22">
+        <v>34</v>
+      </c>
+      <c r="M22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O22" t="s">
+        <v>117</v>
+      </c>
+      <c r="P22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23">
+        <v>28.2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L23">
+        <v>57</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O23" t="s">
+        <v>130</v>
+      </c>
+      <c r="P23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="3">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L24" s="3">
+        <v>59</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O24" t="s">
+        <v>132</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="3">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L25" s="3">
+        <v>65</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L26" s="3">
+        <v>57</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L27" s="3">
+        <v>59</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L28" s="3">
+        <v>63</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29">
+        <v>0.7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L29">
+        <v>49</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O29" t="s">
+        <v>134</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30">
+        <v>13.9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L30">
+        <v>52</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31">
+        <v>1.8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L31">
+        <v>44</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O31" t="s">
+        <v>137</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32">
+        <v>39.6</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L32" s="3">
+        <v>44</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="O32" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33">
+        <v>6.8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L33">
+        <v>7</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O33" t="s">
+        <v>139</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L34" s="3">
+        <v>7</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1" xr:uid="{44ABC253-0668-4FE2-BC14-84FC263B038A}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
+++ b/data_generation/07_soil_degradation/soil_degradation_EFSA_PEC_soil_luel_additional_ai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\07_soil_degradation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780B28F6-6BDB-4517-A139-470B676CE7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A22BF2-A3CF-4A35-AF7F-47B135996B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="6195" windowWidth="19275" windowHeight="7245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle2" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="161">
   <si>
     <t>SFO</t>
   </si>
@@ -277,21 +277,12 @@
     <t>kinetics</t>
   </si>
   <si>
-    <t>normalized max DT50 is 34.145 DFOP (k1=0.6515, k2=0.0203, g=0.2409, p44); Due to short application intervals (≤10d) lab DT50 20.6 d SFO was used as worst case for PECsoil calculations</t>
-  </si>
-  <si>
     <t>j.efsa.2008.167r</t>
   </si>
   <si>
-    <t>7.3 is recalculated from normalized FOMC DT90/3.32  p64</t>
-  </si>
-  <si>
     <t>Copper</t>
   </si>
   <si>
-    <t>No degradation is expected.</t>
-  </si>
-  <si>
     <t>j.efsa.2018.5152</t>
   </si>
   <si>
@@ -307,9 +298,6 @@
     <t>j.efsa.2023.7805_LoEP</t>
   </si>
   <si>
-    <t>no degradation for PEC soil assumed for EFSA PECsoil calculations; default value 1000 d used for PEC sw calculations; wrong DOI in LoEP PDF</t>
-  </si>
-  <si>
     <t>j.efsa.2023.8139_LoEP</t>
   </si>
   <si>
@@ -367,9 +355,6 @@
     <t>FOMC</t>
   </si>
   <si>
-    <t>No pseudo DT50 calculated, as DT90 and DT50 are both &gt;1000d</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -379,9 +364,6 @@
     <t>EFSA LoEP</t>
   </si>
   <si>
-    <t>Worst case lab DT50</t>
-  </si>
-  <si>
     <t>rajo</t>
   </si>
   <si>
@@ -394,9 +376,6 @@
     <t>j.efsa.2015.3973</t>
   </si>
   <si>
-    <t>no degradation considered</t>
-  </si>
-  <si>
     <t>j.efsa.2006.78r</t>
   </si>
   <si>
@@ -433,9 +412,6 @@
     <t>j.efsa.2024.8177_LoEP</t>
   </si>
   <si>
-    <t>listed as correct value to be used in future calculations (53.1 d was used in Conclusion)</t>
-  </si>
-  <si>
     <t>Triclopyr</t>
   </si>
   <si>
@@ -451,38 +427,111 @@
     <t>j.efsa.2011.2091</t>
   </si>
   <si>
-    <t>Longest normalised laboratory value</t>
-  </si>
-  <si>
-    <t>Longest laboratory corrected only for temperature using Q10 = 2.58</t>
-  </si>
-  <si>
     <t>MCPB</t>
   </si>
   <si>
-    <t>20 °C, aerobic (from 2 to 11.4 days; n = 11)</t>
-  </si>
-  <si>
     <t>Rewiev Report LoEP</t>
   </si>
   <si>
-    <t>physchem</t>
-  </si>
-  <si>
     <t>Fluroxypyr-meptyl</t>
   </si>
   <si>
-    <t>MCPB-sodium</t>
-  </si>
-  <si>
     <t>MCPB_RR_2005</t>
+  </si>
+  <si>
+    <t>Maximum non-normalised lab DT50</t>
+  </si>
+  <si>
+    <t>Mean non-normalised lab DT50</t>
+  </si>
+  <si>
+    <t>Propyzamide</t>
+  </si>
+  <si>
+    <t>j.efsa.2016.4554_LoEP</t>
+  </si>
+  <si>
+    <t>Chlorantraniliprole</t>
+  </si>
+  <si>
+    <t>j.efsa.2013.3143</t>
+  </si>
+  <si>
+    <t>Worst-case non-normalised lab DT50 of 0,33 days (p. 42) used in the EFSA conclusion. Worst-case non-normalised field DT50 is 1 day (SFO, p. 47)</t>
+  </si>
+  <si>
+    <t>No degradation for PEC soil assumed for EFSA PECsoil calculations (plateau concentration "not needed"); default value 1000 d used for PEC sw calculations (p. 39); wrong DOI in LoEP PDF</t>
+  </si>
+  <si>
+    <t>Normalized max substitute DT50 is 34.1 d from DFOP k2 (k1=0.6515, k2=0.0203, g=0.2409, p44); Due to short application intervals (≤10d) lab DT50 20.6 d SFO was used as worst case for PECsoil calculations</t>
+  </si>
+  <si>
+    <t>7.3 is recalculated from normalized (Q10 = 2.2) FOMC DT90/3.32  p64</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>Superseded by EFSA conclusion from 2026</t>
+  </si>
+  <si>
+    <t>j.efsa.2026.10150_LoEP</t>
+  </si>
+  <si>
+    <t>"worst case un-normalised laboratory DT90/3.3"</t>
+  </si>
+  <si>
+    <t>"No degradation is expected."</t>
+  </si>
+  <si>
+    <t>"Worst-case from laboratory soil trials, geometric mean of two values (different label positions)"</t>
+  </si>
+  <si>
+    <t>"Worst-case from laboratory soil trials, referenced to pF2 and
+20°C. Geometric mean of two values"</t>
+  </si>
+  <si>
+    <t>Substitute half-life calculated from DFOP k2</t>
+  </si>
+  <si>
+    <t>"worst case first order laboratory value, undertaken at 40-50% MWHC and a temperature of 20 °C"</t>
+  </si>
+  <si>
+    <t>"No degradation considered."</t>
+  </si>
+  <si>
+    <t>Listed as correct value to be used in future calculations (53.1 d was used in Conclusion)</t>
+  </si>
+  <si>
+    <t>"default value from lab studies"</t>
+  </si>
+  <si>
+    <t>"Longest laboratory corrected only for temperature using Q10 = 2.58"</t>
+  </si>
+  <si>
+    <t>"Longest normalised laboratory value"</t>
+  </si>
+  <si>
+    <t>The substitute DT50 calculated from the FOMC parameters (also given for the loamy sand, USA, on p. 40) is 265900 days, which appears unrealistic in the context of the field dissipation data, although e.g. for the Z-isomer in the sandy loam, UK, a substitue DT50 of   29300 days is obtained in the lab. It is unclear why no worst-case non-normalised field results were used.</t>
+  </si>
+  <si>
+    <t>Not clear if arithmetic or geometric mean</t>
+  </si>
+  <si>
+    <t>Maximum normalised worst case lab DT50 (Marietta sandy loam) used for PECsoil calculations by EFSA</t>
+  </si>
+  <si>
+    <t>Maximum non-normalised field DT50</t>
+  </si>
+  <si>
+    <t>Longer half-lives observed in the field should not be ignored</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,30 +549,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -538,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -548,9 +584,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -831,18 +865,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ABC253-0668-4FE2-BC14-84FC263B038A}">
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="24" style="3" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="3" customWidth="1"/>
     <col min="3" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="7" width="6.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="3" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="3" customWidth="1"/>
     <col min="9" max="10" width="6.85546875" style="3" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="12" width="8.140625" customWidth="1"/>
     <col min="14" max="14" width="33.140625" customWidth="1"/>
+    <col min="15" max="15" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -850,7 +887,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>76</v>
@@ -898,111 +935,127 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:17" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2">
+        <v>105</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" s="3">
+        <v>53</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
         <v>74</v>
       </c>
-      <c r="L2">
+      <c r="L3">
         <v>47</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L3" s="4">
-        <v>39</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>34</v>
+        <v>106</v>
+      </c>
+      <c r="O3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="4">
-        <v>20.6</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L4" s="4">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>33</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="P4" s="4" t="s">
         <v>34</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C5" s="4">
-        <v>226</v>
+        <v>20.6</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L5" s="4">
         <v>57</v>
@@ -1011,706 +1064,768 @@
         <v>33</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="P5" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>73</v>
+      <c r="Q5" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="6">
-        <v>7.3</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>79</v>
+        <v>105</v>
+      </c>
+      <c r="C6" s="4">
+        <v>226</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="L6" s="4">
-        <v>70</v>
-      </c>
-      <c r="M6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>34</v>
+        <v>106</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7.3</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="K7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L7" s="4">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>111</v>
+        <v>143</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>81</v>
+      <c r="Q7" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" t="s">
-        <v>83</v>
-      </c>
-      <c r="L8">
-        <v>59</v>
+        <v>105</v>
+      </c>
+      <c r="C8" s="3">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L8" s="4">
+        <v>68</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O8" t="s">
-        <v>82</v>
+        <v>106</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>34</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="Q8" s="4"/>
     </row>
     <row r="9" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9">
-        <v>28.4</v>
-      </c>
-      <c r="D9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9">
-        <v>78</v>
+        <v>81</v>
+      </c>
+      <c r="L9" s="4">
+        <v>40</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P9" t="s">
-        <v>34</v>
+        <v>106</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="L10">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
+      </c>
+      <c r="O10" t="s">
+        <v>146</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>86</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="3">
-        <v>4.29</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L11" s="3">
-        <v>56</v>
+        <v>105</v>
+      </c>
+      <c r="C11">
+        <v>28.4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11">
+        <v>78</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>34</v>
+        <v>106</v>
+      </c>
+      <c r="P11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C12">
-        <v>139.5</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="L12">
-        <v>41</v>
-      </c>
-      <c r="M12" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="P12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>97</v>
+      <c r="Q12" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13">
-        <v>184.9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
-        <v>102</v>
-      </c>
-      <c r="L13">
-        <v>40</v>
-      </c>
-      <c r="M13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4.29</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L13" s="3">
+        <v>56</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P13" t="s">
-        <v>34</v>
+        <v>106</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C14">
-        <v>29.6</v>
+        <v>139.5</v>
       </c>
       <c r="D14" t="s">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M14" t="s">
         <v>33</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="P14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="P14" t="s">
         <v>34</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C15">
-        <f>LN(2)/H15</f>
-        <v>533.19013889226562</v>
+        <v>184.9</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0.19139999999999999</v>
+        <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L15">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M15" t="s">
         <v>33</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>34</v>
+        <v>106</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="P15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16">
+        <v>29.6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L16">
+        <v>37</v>
+      </c>
+      <c r="M16" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17">
+        <v>533.20000000000005</v>
+      </c>
+      <c r="D17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.19139999999999999</v>
+      </c>
+      <c r="K17" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="L17">
+        <v>33</v>
+      </c>
+      <c r="M17" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O17" t="s">
+        <v>149</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.18084</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2.6067999999999998</v>
+      </c>
+      <c r="K18" t="s">
+        <v>102</v>
+      </c>
+      <c r="L18">
+        <v>56</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="3">
+        <v>136</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L19" s="3">
+        <v>60</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20">
+        <v>10.19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="L20">
+        <v>64</v>
+      </c>
+      <c r="M20" t="s">
+        <v>33</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O20" t="s">
+        <v>113</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="3">
+        <v>43</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L21" s="3">
+        <v>48</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>112</v>
+      </c>
+      <c r="L22">
+        <v>56</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="3">
+        <v>20</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L23" s="3">
+        <v>56</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0.18084</v>
-      </c>
-      <c r="F16" s="3">
-        <v>2.6067999999999998</v>
-      </c>
-      <c r="K16" t="s">
-        <v>106</v>
-      </c>
-      <c r="L16">
-        <v>56</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="3">
-        <v>136</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L17" s="3">
-        <v>60</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="L24">
+        <v>34</v>
+      </c>
+      <c r="M24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O24" t="s">
+        <v>151</v>
+      </c>
+      <c r="P24" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>123</v>
       </c>
-      <c r="C18">
-        <v>10.19</v>
-      </c>
-      <c r="D18" t="s">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L18">
-        <v>64</v>
-      </c>
-      <c r="M18" t="s">
-        <v>33</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O18" t="s">
+      <c r="B25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25">
+        <v>28.2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L25">
+        <v>57</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O25" t="s">
+        <v>152</v>
+      </c>
+      <c r="P25" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="P18" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="C26" s="3">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="3">
+        <v>59</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O26" t="s">
+        <v>124</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="3">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L27" s="3">
+        <v>65</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O27" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" s="3">
-        <v>43</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="s">
+      <c r="P27" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="L19" s="3">
-        <v>56</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20">
-        <v>20</v>
-      </c>
-      <c r="D20" t="s">
-        <v>0</v>
-      </c>
-      <c r="K20" t="s">
-        <v>119</v>
-      </c>
-      <c r="L20">
-        <v>56</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="3">
-        <v>20</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L21" s="3">
-        <v>56</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K22" t="s">
-        <v>116</v>
-      </c>
-      <c r="L22">
-        <v>34</v>
-      </c>
-      <c r="M22" t="s">
-        <v>33</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O22" t="s">
-        <v>117</v>
-      </c>
-      <c r="P22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23">
-        <v>28.2</v>
-      </c>
-      <c r="D23" t="s">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="L23">
-        <v>57</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O23" t="s">
-        <v>130</v>
-      </c>
-      <c r="P23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="3">
-        <v>9.1300000000000008</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="L24" s="3">
-        <v>59</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O24" t="s">
-        <v>132</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C25" s="3">
-        <v>9.1300000000000008</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="L25" s="3">
-        <v>65</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="L26" s="3">
-        <v>57</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O26"/>
-      <c r="P26" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C27" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="L27" s="3">
-        <v>59</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="B28" s="3" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C28" s="3">
         <v>1.5</v>
@@ -1719,211 +1834,354 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L28" s="3">
+        <v>57</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O28" t="s">
+        <v>153</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L29" s="3">
+        <v>59</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L30" s="3">
+        <v>63</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31">
+        <v>0.7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L31">
+        <v>49</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O31" t="s">
+        <v>126</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32">
+        <v>13.9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L32">
+        <v>52</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33">
+        <v>1.8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L33">
+        <v>44</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O33" t="s">
+        <v>154</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34">
+        <v>39.6</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L34" s="3">
+        <v>44</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O34" t="s">
+        <v>155</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35">
+        <v>11.4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="L35">
+        <v>7</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N35" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="L28" s="3">
-        <v>63</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O28" s="3" t="s">
+      <c r="P35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="P28" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>142</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29">
-        <v>0.7</v>
-      </c>
-      <c r="D29" t="s">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
+      <c r="B36" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="L36" s="3">
+        <v>7</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37">
+        <v>195.2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
         <v>135</v>
       </c>
-      <c r="L29">
-        <v>49</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O29" t="s">
-        <v>134</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30">
-        <v>13.9</v>
-      </c>
-      <c r="D30" t="s">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="L30">
-        <v>52</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31">
-        <v>1.8</v>
-      </c>
-      <c r="D31" t="s">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="L31">
-        <v>44</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O31" t="s">
+      <c r="L37">
+        <v>37</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>1378</v>
+      </c>
+      <c r="D38" t="s">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
         <v>137</v>
       </c>
-      <c r="P31" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C32">
-        <v>39.6</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="L32" s="3">
-        <v>44</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O32" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>138</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C33">
-        <v>6.8</v>
-      </c>
-      <c r="D33" t="s">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L33">
-        <v>7</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="O33" t="s">
-        <v>139</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="3">
-        <v>6.8</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L34" s="3">
-        <v>7</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>34</v>
+      <c r="L38">
+        <v>56</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O38" t="s">
+        <v>158</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
